--- a/education_forms/030_university_faculty_research_impact_assessment--education_forms.xlsx
+++ b/education_forms/030_university_faculty_research_impact_assessment--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>research_experts</t>
+          <t>research_experts_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Research Experts</t>
+          <t>Research Experts 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>research_leads</t>
+          <t>research_leads_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Research Leads</t>
+          <t>Research Leads 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>research_participates</t>
+          <t>research_participates_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Research Participates</t>
+          <t>Research Participates 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>research_experts_choices</t>
+          <t>research_experts_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>research_experts_choices</t>
+          <t>research_experts_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>research_experts_choices</t>
+          <t>research_experts_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>research_leads_choices</t>
+          <t>research_leads_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>research_leads_choices</t>
+          <t>research_leads_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,7 +2027,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>research_leads_choices</t>
+          <t>research_leads_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>research_participates_choices</t>
+          <t>research_participates_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>research_participates_choices</t>
+          <t>research_participates_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>research_participates_choices</t>
+          <t>research_participates_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
